--- a/storage/exports/rekap_reject_10_2025.xlsx
+++ b/storage/exports/rekap_reject_10_2025.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\willi\Project\cek-gambar-astras\storage\exports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0476F323-6DA9-423F-9A6B-6FB8B2FF709F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71FD4B25-B1EA-4871-9135-2D6609A39941}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA KLAIM KPB October" sheetId="1" r:id="rId1"/>
@@ -26951,7 +26951,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:J337"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -26997,7 +26996,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -27029,7 +27028,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="3" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -27061,7 +27060,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="4" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -27093,7 +27092,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="5" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -27125,7 +27124,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="6" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -27157,7 +27156,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="7" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -27189,7 +27188,7 @@
         <v>1216</v>
       </c>
     </row>
-    <row r="8" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -27221,7 +27220,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="9" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -27253,7 +27252,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="10" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -27285,7 +27284,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="11" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -27317,7 +27316,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="12" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>11</v>
       </c>
@@ -27349,7 +27348,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="13" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -27381,7 +27380,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="14" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -27413,7 +27412,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="15" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -27445,7 +27444,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="16" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -27477,7 +27476,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="17" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -27509,7 +27508,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="18" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -27541,7 +27540,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="19" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -27573,7 +27572,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="20" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -27605,7 +27604,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="21" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -27637,7 +27636,7 @@
         <v>1242</v>
       </c>
     </row>
-    <row r="22" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -27669,7 +27668,7 @@
         <v>1244</v>
       </c>
     </row>
-    <row r="23" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -27701,7 +27700,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="24" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -27733,7 +27732,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="25" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -27765,7 +27764,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="26" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -27797,7 +27796,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="27" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -27829,7 +27828,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="28" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -27861,7 +27860,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="29" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -27893,7 +27892,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="30" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -27925,7 +27924,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="31" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -27957,7 +27956,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="32" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -27989,7 +27988,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="33" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -28021,7 +28020,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="34" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -28053,7 +28052,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="35" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -28085,7 +28084,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="36" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -28117,7 +28116,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="37" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -28149,7 +28148,7 @@
         <v>1266</v>
       </c>
     </row>
-    <row r="38" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -28181,7 +28180,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="39" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -28213,7 +28212,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="40" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -28245,7 +28244,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="41" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A41" s="1">
         <v>40</v>
       </c>
@@ -28277,7 +28276,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="42" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A42" s="1">
         <v>41</v>
       </c>
@@ -28309,7 +28308,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="43" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A43" s="1">
         <v>42</v>
       </c>
@@ -28341,7 +28340,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="44" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A44" s="1">
         <v>43</v>
       </c>
@@ -28373,7 +28372,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="45" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A45" s="1">
         <v>44</v>
       </c>
@@ -28405,7 +28404,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="46" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A46" s="1">
         <v>45</v>
       </c>
@@ -28437,7 +28436,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="47" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A47" s="1">
         <v>46</v>
       </c>
@@ -28469,7 +28468,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="48" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A48" s="1">
         <v>47</v>
       </c>
@@ -28501,7 +28500,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="49" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="1">
         <v>48</v>
       </c>
@@ -28533,7 +28532,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="50" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="1">
         <v>49</v>
       </c>
@@ -28565,7 +28564,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="51" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="1">
         <v>50</v>
       </c>
@@ -28597,7 +28596,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="52" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="1">
         <v>51</v>
       </c>
@@ -28629,7 +28628,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="53" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="1">
         <v>52</v>
       </c>
@@ -28661,7 +28660,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="54" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="1">
         <v>53</v>
       </c>
@@ -28693,7 +28692,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="55" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="1">
         <v>54</v>
       </c>
@@ -28725,7 +28724,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="56" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="1">
         <v>55</v>
       </c>
@@ -28757,7 +28756,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="57" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="1">
         <v>56</v>
       </c>
@@ -28789,7 +28788,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="58" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="1">
         <v>57</v>
       </c>
@@ -28821,7 +28820,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="59" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="1">
         <v>58</v>
       </c>
@@ -28853,7 +28852,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="60" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="1">
         <v>59</v>
       </c>
@@ -28885,7 +28884,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="61" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61" s="1">
         <v>60</v>
       </c>
@@ -28917,7 +28916,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="62" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62" s="1">
         <v>61</v>
       </c>
@@ -28949,7 +28948,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="63" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63" s="1">
         <v>62</v>
       </c>
@@ -28981,7 +28980,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="64" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64" s="1">
         <v>63</v>
       </c>
@@ -29013,7 +29012,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="65" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A65" s="1">
         <v>64</v>
       </c>
@@ -29045,7 +29044,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="66" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A66" s="1">
         <v>65</v>
       </c>
@@ -29077,7 +29076,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="67" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A67" s="1">
         <v>66</v>
       </c>
@@ -29109,7 +29108,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="68" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A68" s="1">
         <v>67</v>
       </c>
@@ -29141,7 +29140,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="69" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A69" s="1">
         <v>68</v>
       </c>
@@ -29173,7 +29172,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="70" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A70" s="1">
         <v>69</v>
       </c>
@@ -29205,7 +29204,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="71" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A71" s="1">
         <v>70</v>
       </c>
@@ -29237,7 +29236,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="72" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A72" s="1">
         <v>71</v>
       </c>
@@ -29269,7 +29268,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="73" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A73" s="1">
         <v>72</v>
       </c>
@@ -29301,7 +29300,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="74" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A74" s="1">
         <v>73</v>
       </c>
@@ -29333,7 +29332,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="75" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A75" s="1">
         <v>74</v>
       </c>
@@ -29365,7 +29364,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="76" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A76" s="1">
         <v>75</v>
       </c>
@@ -29397,7 +29396,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="77" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A77" s="1">
         <v>76</v>
       </c>
@@ -29429,7 +29428,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="78" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A78" s="1">
         <v>77</v>
       </c>
@@ -29461,7 +29460,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="79" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A79" s="1">
         <v>78</v>
       </c>
@@ -29493,7 +29492,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="80" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A80" s="1">
         <v>79</v>
       </c>
@@ -29525,7 +29524,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="81" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A81" s="1">
         <v>80</v>
       </c>
@@ -29557,7 +29556,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="82" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A82" s="1">
         <v>81</v>
       </c>
@@ -29589,7 +29588,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="83" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A83" s="1">
         <v>82</v>
       </c>
@@ -29621,7 +29620,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="84" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A84" s="1">
         <v>83</v>
       </c>
@@ -29653,7 +29652,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="85" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A85" s="1">
         <v>84</v>
       </c>
@@ -29685,7 +29684,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="86" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A86" s="1">
         <v>85</v>
       </c>
@@ -29717,7 +29716,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="87" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A87" s="1">
         <v>86</v>
       </c>
@@ -29749,7 +29748,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="88" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A88" s="1">
         <v>87</v>
       </c>
@@ -29781,7 +29780,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="89" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A89" s="1">
         <v>88</v>
       </c>
@@ -29813,7 +29812,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="90" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A90" s="1">
         <v>89</v>
       </c>
@@ -29845,7 +29844,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="91" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A91" s="1">
         <v>90</v>
       </c>
@@ -29877,7 +29876,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="92" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A92" s="1">
         <v>91</v>
       </c>
@@ -29909,7 +29908,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="93" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A93" s="1">
         <v>92</v>
       </c>
@@ -29941,7 +29940,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="94" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A94" s="1">
         <v>93</v>
       </c>
@@ -29973,7 +29972,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="95" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A95" s="1">
         <v>94</v>
       </c>
@@ -30005,7 +30004,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="96" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A96" s="1">
         <v>95</v>
       </c>
@@ -30037,7 +30036,7 @@
         <v>1252</v>
       </c>
     </row>
-    <row r="97" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A97" s="1">
         <v>96</v>
       </c>
@@ -30069,7 +30068,7 @@
         <v>1258</v>
       </c>
     </row>
-    <row r="98" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A98" s="1">
         <v>97</v>
       </c>
@@ -30101,7 +30100,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="99" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A99" s="1">
         <v>98</v>
       </c>
@@ -30133,7 +30132,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="100" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A100" s="1">
         <v>99</v>
       </c>
@@ -30165,7 +30164,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="101" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A101" s="1">
         <v>100</v>
       </c>
@@ -30197,7 +30196,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="102" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A102" s="1">
         <v>101</v>
       </c>
@@ -30229,7 +30228,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="103" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A103" s="1">
         <v>102</v>
       </c>
@@ -30261,7 +30260,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="104" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A104" s="1">
         <v>103</v>
       </c>
@@ -30293,7 +30292,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="105" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A105" s="1">
         <v>104</v>
       </c>
@@ -30325,7 +30324,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="106" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A106" s="1">
         <v>105</v>
       </c>
@@ -30357,7 +30356,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="107" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A107" s="1">
         <v>106</v>
       </c>
@@ -30389,7 +30388,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="108" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A108" s="1">
         <v>107</v>
       </c>
@@ -30421,7 +30420,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="109" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A109" s="1">
         <v>108</v>
       </c>
@@ -30453,7 +30452,7 @@
         <v>1212</v>
       </c>
     </row>
-    <row r="110" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A110" s="1">
         <v>109</v>
       </c>
@@ -30485,7 +30484,7 @@
         <v>1354</v>
       </c>
     </row>
-    <row r="111" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A111" s="1">
         <v>110</v>
       </c>
@@ -30517,7 +30516,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="112" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A112" s="1">
         <v>111</v>
       </c>
@@ -30549,7 +30548,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="113" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A113" s="1">
         <v>112</v>
       </c>
@@ -30581,7 +30580,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="114" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A114" s="1">
         <v>113</v>
       </c>
@@ -30613,7 +30612,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="115" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A115" s="1">
         <v>114</v>
       </c>
@@ -30645,7 +30644,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="116" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A116" s="1">
         <v>115</v>
       </c>
@@ -30677,7 +30676,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="117" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A117" s="1">
         <v>116</v>
       </c>
@@ -30709,7 +30708,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="118" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A118" s="1">
         <v>117</v>
       </c>
@@ -30741,7 +30740,7 @@
         <v>1365</v>
       </c>
     </row>
-    <row r="119" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A119" s="1">
         <v>118</v>
       </c>
@@ -30773,7 +30772,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="120" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A120" s="1">
         <v>119</v>
       </c>
@@ -30805,7 +30804,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="121" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A121" s="1">
         <v>120</v>
       </c>
@@ -30837,7 +30836,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="122" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A122" s="1">
         <v>121</v>
       </c>
@@ -30869,7 +30868,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="123" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A123" s="1">
         <v>122</v>
       </c>
@@ -30901,7 +30900,7 @@
         <v>1373</v>
       </c>
     </row>
-    <row r="124" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A124" s="1">
         <v>123</v>
       </c>
@@ -30933,7 +30932,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="125" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A125" s="1">
         <v>124</v>
       </c>
@@ -30965,7 +30964,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="126" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A126" s="1">
         <v>125</v>
       </c>
@@ -30997,7 +30996,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="127" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A127" s="1">
         <v>126</v>
       </c>
@@ -31029,7 +31028,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="128" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A128" s="1">
         <v>127</v>
       </c>
@@ -31061,7 +31060,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="129" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A129" s="1">
         <v>128</v>
       </c>
@@ -31093,7 +31092,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="130" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A130" s="1">
         <v>129</v>
       </c>
@@ -31125,7 +31124,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="131" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A131" s="1">
         <v>130</v>
       </c>
@@ -31157,7 +31156,7 @@
         <v>1385</v>
       </c>
     </row>
-    <row r="132" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A132" s="1">
         <v>131</v>
       </c>
@@ -31189,7 +31188,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="133" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A133" s="1">
         <v>132</v>
       </c>
@@ -31221,7 +31220,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="134" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A134" s="1">
         <v>133</v>
       </c>
@@ -31253,7 +31252,7 @@
         <v>1391</v>
       </c>
     </row>
-    <row r="135" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A135" s="1">
         <v>134</v>
       </c>
@@ -31285,7 +31284,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="136" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A136" s="1">
         <v>135</v>
       </c>
@@ -31317,7 +31316,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="137" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A137" s="1">
         <v>136</v>
       </c>
@@ -31349,7 +31348,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="138" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A138" s="1">
         <v>137</v>
       </c>
@@ -31381,7 +31380,7 @@
         <v>1207</v>
       </c>
     </row>
-    <row r="139" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A139" s="1">
         <v>138</v>
       </c>
@@ -31413,7 +31412,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="140" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A140" s="1">
         <v>139</v>
       </c>
@@ -31445,7 +31444,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="141" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A141" s="1">
         <v>140</v>
       </c>
@@ -31477,7 +31476,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="142" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A142" s="1">
         <v>141</v>
       </c>
@@ -31509,7 +31508,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="143" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A143" s="1">
         <v>142</v>
       </c>
@@ -31541,7 +31540,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="144" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A144" s="1">
         <v>143</v>
       </c>
@@ -31573,7 +31572,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="145" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A145" s="1">
         <v>144</v>
       </c>
@@ -31605,7 +31604,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="146" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A146" s="1">
         <v>145</v>
       </c>
@@ -31637,7 +31636,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="147" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A147" s="1">
         <v>146</v>
       </c>
@@ -31669,7 +31668,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="148" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A148" s="1">
         <v>147</v>
       </c>
@@ -31701,7 +31700,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="149" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A149" s="1">
         <v>148</v>
       </c>
@@ -31733,7 +31732,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="150" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A150" s="1">
         <v>149</v>
       </c>
@@ -31765,7 +31764,7 @@
         <v>1413</v>
       </c>
     </row>
-    <row r="151" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A151" s="1">
         <v>150</v>
       </c>
@@ -31797,7 +31796,7 @@
         <v>1415</v>
       </c>
     </row>
-    <row r="152" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A152" s="1">
         <v>151</v>
       </c>
@@ -31829,7 +31828,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="153" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A153" s="1">
         <v>152</v>
       </c>
@@ -31861,7 +31860,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="154" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A154" s="1">
         <v>153</v>
       </c>
@@ -31893,7 +31892,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="155" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A155" s="1">
         <v>154</v>
       </c>
@@ -31925,7 +31924,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="156" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A156" s="1">
         <v>155</v>
       </c>
@@ -31957,7 +31956,7 @@
         <v>1419</v>
       </c>
     </row>
-    <row r="157" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A157" s="1">
         <v>156</v>
       </c>
@@ -31989,7 +31988,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="158" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A158" s="1">
         <v>157</v>
       </c>
@@ -32021,7 +32020,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="159" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A159" s="1">
         <v>158</v>
       </c>
@@ -32053,7 +32052,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="160" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A160" s="1">
         <v>159</v>
       </c>
@@ -32085,7 +32084,7 @@
         <v>1427</v>
       </c>
     </row>
-    <row r="161" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A161" s="1">
         <v>160</v>
       </c>
@@ -32117,7 +32116,7 @@
         <v>1428</v>
       </c>
     </row>
-    <row r="162" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A162" s="1">
         <v>161</v>
       </c>
@@ -32149,7 +32148,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="163" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A163" s="1">
         <v>162</v>
       </c>
@@ -32181,7 +32180,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="164" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A164" s="1">
         <v>163</v>
       </c>
@@ -32213,7 +32212,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="165" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A165" s="1">
         <v>164</v>
       </c>
@@ -32245,7 +32244,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="166" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A166" s="1">
         <v>165</v>
       </c>
@@ -32277,7 +32276,7 @@
         <v>1406</v>
       </c>
     </row>
-    <row r="167" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A167" s="1">
         <v>166</v>
       </c>
@@ -32309,7 +32308,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="168" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A168" s="1">
         <v>167</v>
       </c>
@@ -32341,7 +32340,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="169" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A169" s="1">
         <v>168</v>
       </c>
@@ -32373,7 +32372,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="170" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A170" s="1">
         <v>169</v>
       </c>
@@ -32405,7 +32404,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="171" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A171" s="1">
         <v>170</v>
       </c>
@@ -32437,7 +32436,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="172" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A172" s="1">
         <v>171</v>
       </c>
@@ -32469,7 +32468,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="173" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A173" s="1">
         <v>172</v>
       </c>
@@ -32501,7 +32500,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="174" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A174" s="1">
         <v>173</v>
       </c>
@@ -32533,7 +32532,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="175" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A175" s="1">
         <v>174</v>
       </c>
@@ -32565,7 +32564,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="176" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A176" s="1">
         <v>175</v>
       </c>
@@ -32597,7 +32596,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="177" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A177" s="1">
         <v>176</v>
       </c>
@@ -32629,7 +32628,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="178" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A178" s="1">
         <v>177</v>
       </c>
@@ -32661,7 +32660,7 @@
         <v>1451</v>
       </c>
     </row>
-    <row r="179" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A179" s="1">
         <v>178</v>
       </c>
@@ -32693,7 +32692,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="180" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A180" s="1">
         <v>179</v>
       </c>
@@ -32725,7 +32724,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="181" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A181" s="1">
         <v>180</v>
       </c>
@@ -32757,7 +32756,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="182" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A182" s="1">
         <v>181</v>
       </c>
@@ -32789,7 +32788,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="183" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A183" s="1">
         <v>182</v>
       </c>
@@ -32821,7 +32820,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="184" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A184" s="1">
         <v>183</v>
       </c>
@@ -32853,7 +32852,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="185" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A185" s="1">
         <v>184</v>
       </c>
@@ -32885,7 +32884,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="186" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A186" s="1">
         <v>185</v>
       </c>
@@ -32917,7 +32916,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="187" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A187" s="1">
         <v>186</v>
       </c>
@@ -32949,7 +32948,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="188" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A188" s="1">
         <v>187</v>
       </c>
@@ -32981,7 +32980,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="189" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A189" s="1">
         <v>188</v>
       </c>
@@ -33013,7 +33012,7 @@
         <v>1469</v>
       </c>
     </row>
-    <row r="190" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A190" s="1">
         <v>189</v>
       </c>
@@ -33045,7 +33044,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="191" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A191" s="1">
         <v>190</v>
       </c>
@@ -33077,7 +33076,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="192" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A192" s="1">
         <v>191</v>
       </c>
@@ -33109,7 +33108,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="193" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A193" s="1">
         <v>192</v>
       </c>
@@ -33141,7 +33140,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="194" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A194" s="1">
         <v>193</v>
       </c>
@@ -33173,7 +33172,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="195" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A195" s="1">
         <v>194</v>
       </c>
@@ -33205,7 +33204,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="196" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A196" s="1">
         <v>195</v>
       </c>
@@ -33237,7 +33236,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="197" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A197" s="1">
         <v>196</v>
       </c>
@@ -33269,7 +33268,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="198" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A198" s="1">
         <v>197</v>
       </c>
@@ -33301,7 +33300,7 @@
         <v>1481</v>
       </c>
     </row>
-    <row r="199" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A199" s="1">
         <v>198</v>
       </c>
@@ -33333,7 +33332,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="200" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A200" s="1">
         <v>199</v>
       </c>
@@ -33365,7 +33364,7 @@
         <v>1484</v>
       </c>
     </row>
-    <row r="201" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A201" s="1">
         <v>200</v>
       </c>
@@ -33397,7 +33396,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="202" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A202" s="1">
         <v>201</v>
       </c>
@@ -33429,7 +33428,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="203" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A203" s="1">
         <v>202</v>
       </c>
@@ -33461,7 +33460,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="204" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A204" s="1">
         <v>203</v>
       </c>
@@ -33493,7 +33492,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="205" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A205" s="1">
         <v>204</v>
       </c>
@@ -33525,7 +33524,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="206" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A206" s="1">
         <v>205</v>
       </c>
@@ -33557,7 +33556,7 @@
         <v>1446</v>
       </c>
     </row>
-    <row r="207" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A207" s="1">
         <v>206</v>
       </c>
@@ -33589,7 +33588,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="208" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A208" s="1">
         <v>207</v>
       </c>
@@ -33621,7 +33620,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="209" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A209" s="1">
         <v>208</v>
       </c>
@@ -33653,7 +33652,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="210" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A210" s="1">
         <v>209</v>
       </c>
@@ -33685,7 +33684,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="211" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A211" s="1">
         <v>210</v>
       </c>
@@ -33717,7 +33716,7 @@
         <v>1500</v>
       </c>
     </row>
-    <row r="212" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A212" s="1">
         <v>211</v>
       </c>
@@ -33749,7 +33748,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="213" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A213" s="1">
         <v>212</v>
       </c>
@@ -33781,7 +33780,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="214" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A214" s="1">
         <v>213</v>
       </c>
@@ -33813,7 +33812,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="215" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A215" s="1">
         <v>214</v>
       </c>
@@ -33845,7 +33844,7 @@
         <v>1507</v>
       </c>
     </row>
-    <row r="216" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A216" s="1">
         <v>215</v>
       </c>
@@ -33877,7 +33876,7 @@
         <v>1509</v>
       </c>
     </row>
-    <row r="217" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A217" s="1">
         <v>216</v>
       </c>
@@ -33909,7 +33908,7 @@
         <v>1511</v>
       </c>
     </row>
-    <row r="218" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A218" s="1">
         <v>217</v>
       </c>
@@ -33941,7 +33940,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="219" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A219" s="1">
         <v>218</v>
       </c>
@@ -33973,7 +33972,7 @@
         <v>1514</v>
       </c>
     </row>
-    <row r="220" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A220" s="1">
         <v>219</v>
       </c>
@@ -34005,7 +34004,7 @@
         <v>1516</v>
       </c>
     </row>
-    <row r="221" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A221" s="1">
         <v>220</v>
       </c>
@@ -34037,7 +34036,7 @@
         <v>1519</v>
       </c>
     </row>
-    <row r="222" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A222" s="1">
         <v>221</v>
       </c>
@@ -34069,7 +34068,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="223" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A223" s="1">
         <v>222</v>
       </c>
@@ -34101,7 +34100,7 @@
         <v>1523</v>
       </c>
     </row>
-    <row r="224" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A224" s="1">
         <v>223</v>
       </c>
@@ -34133,7 +34132,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="225" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A225" s="1">
         <v>224</v>
       </c>
@@ -34165,7 +34164,7 @@
         <v>1527</v>
       </c>
     </row>
-    <row r="226" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A226" s="1">
         <v>225</v>
       </c>
@@ -34197,7 +34196,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="227" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A227" s="1">
         <v>226</v>
       </c>
@@ -34229,7 +34228,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="228" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A228" s="1">
         <v>227</v>
       </c>
@@ -34261,7 +34260,7 @@
         <v>1532</v>
       </c>
     </row>
-    <row r="229" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A229" s="1">
         <v>228</v>
       </c>
@@ -34293,7 +34292,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="230" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A230" s="1">
         <v>229</v>
       </c>
@@ -34325,7 +34324,7 @@
         <v>1536</v>
       </c>
     </row>
-    <row r="231" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A231" s="1">
         <v>230</v>
       </c>
@@ -34357,7 +34356,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="232" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A232" s="1">
         <v>231</v>
       </c>
@@ -34389,7 +34388,7 @@
         <v>1539</v>
       </c>
     </row>
-    <row r="233" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A233" s="1">
         <v>232</v>
       </c>
@@ -34421,7 +34420,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="234" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A234" s="1">
         <v>233</v>
       </c>
@@ -34453,7 +34452,7 @@
         <v>1542</v>
       </c>
     </row>
-    <row r="235" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A235" s="1">
         <v>234</v>
       </c>
@@ -34485,7 +34484,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="236" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A236" s="1">
         <v>235</v>
       </c>
@@ -34517,7 +34516,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="237" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A237" s="1">
         <v>236</v>
       </c>
@@ -34549,7 +34548,7 @@
         <v>1546</v>
       </c>
     </row>
-    <row r="238" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A238" s="1">
         <v>237</v>
       </c>
@@ -34581,7 +34580,7 @@
         <v>1548</v>
       </c>
     </row>
-    <row r="239" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A239" s="1">
         <v>238</v>
       </c>
@@ -34613,7 +34612,7 @@
         <v>1550</v>
       </c>
     </row>
-    <row r="240" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A240" s="1">
         <v>239</v>
       </c>
@@ -34645,7 +34644,7 @@
         <v>1552</v>
       </c>
     </row>
-    <row r="241" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A241" s="1">
         <v>240</v>
       </c>
@@ -34677,7 +34676,7 @@
         <v>1554</v>
       </c>
     </row>
-    <row r="242" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A242" s="1">
         <v>241</v>
       </c>
@@ -34709,7 +34708,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="243" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A243" s="1">
         <v>242</v>
       </c>
@@ -34741,7 +34740,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="244" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A244" s="1">
         <v>243</v>
       </c>
@@ -34773,7 +34772,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="245" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A245" s="1">
         <v>244</v>
       </c>
@@ -34805,7 +34804,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="246" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A246" s="1">
         <v>245</v>
       </c>
@@ -34837,7 +34836,7 @@
         <v>1563</v>
       </c>
     </row>
-    <row r="247" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A247" s="1">
         <v>246</v>
       </c>
@@ -34869,7 +34868,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="248" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A248" s="1">
         <v>247</v>
       </c>
@@ -34901,7 +34900,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="249" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A249" s="1">
         <v>248</v>
       </c>
@@ -34933,7 +34932,7 @@
         <v>1570</v>
       </c>
     </row>
-    <row r="250" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A250" s="1">
         <v>249</v>
       </c>
@@ -34965,7 +34964,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="251" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A251" s="1">
         <v>250</v>
       </c>
@@ -34997,7 +34996,7 @@
         <v>1574</v>
       </c>
     </row>
-    <row r="252" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A252" s="1">
         <v>251</v>
       </c>
@@ -35029,7 +35028,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="253" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A253" s="1">
         <v>252</v>
       </c>
@@ -35061,7 +35060,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="254" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A254" s="1">
         <v>253</v>
       </c>
@@ -35093,7 +35092,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="255" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A255" s="1">
         <v>254</v>
       </c>
@@ -35125,7 +35124,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="256" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A256" s="1">
         <v>255</v>
       </c>
@@ -35157,7 +35156,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="257" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A257" s="1">
         <v>256</v>
       </c>
@@ -35189,7 +35188,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="258" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A258" s="1">
         <v>257</v>
       </c>
@@ -35221,7 +35220,7 @@
         <v>1586</v>
       </c>
     </row>
-    <row r="259" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A259" s="1">
         <v>258</v>
       </c>
@@ -35253,7 +35252,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="260" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A260" s="1">
         <v>259</v>
       </c>
@@ -35285,7 +35284,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="261" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A261" s="1">
         <v>260</v>
       </c>
@@ -35317,7 +35316,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="262" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A262" s="1">
         <v>261</v>
       </c>
@@ -35349,7 +35348,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="263" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A263" s="1">
         <v>262</v>
       </c>
@@ -35381,7 +35380,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="264" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A264" s="1">
         <v>263</v>
       </c>
@@ -35413,7 +35412,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="265" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A265" s="1">
         <v>264</v>
       </c>
@@ -35445,7 +35444,7 @@
         <v>1590</v>
       </c>
     </row>
-    <row r="266" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A266" s="1">
         <v>265</v>
       </c>
@@ -35477,7 +35476,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="267" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A267" s="1">
         <v>266</v>
       </c>
@@ -35509,7 +35508,7 @@
         <v>1601</v>
       </c>
     </row>
-    <row r="268" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A268" s="1">
         <v>267</v>
       </c>
@@ -35541,7 +35540,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="269" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A269" s="1">
         <v>268</v>
       </c>
@@ -35573,7 +35572,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="270" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A270" s="1">
         <v>269</v>
       </c>
@@ -35605,7 +35604,7 @@
         <v>1606</v>
       </c>
     </row>
-    <row r="271" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A271" s="1">
         <v>270</v>
       </c>
@@ -35637,7 +35636,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="272" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A272" s="1">
         <v>271</v>
       </c>
@@ -35669,7 +35668,7 @@
         <v>1610</v>
       </c>
     </row>
-    <row r="273" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A273" s="1">
         <v>272</v>
       </c>
@@ -35701,7 +35700,7 @@
         <v>1612</v>
       </c>
     </row>
-    <row r="274" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A274" s="1">
         <v>273</v>
       </c>
@@ -35733,7 +35732,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="275" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A275" s="1">
         <v>274</v>
       </c>
@@ -35765,7 +35764,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="276" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A276" s="1">
         <v>275</v>
       </c>
@@ -35797,7 +35796,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="277" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A277" s="1">
         <v>276</v>
       </c>
@@ -35829,7 +35828,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="278" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A278" s="1">
         <v>277</v>
       </c>
@@ -35861,7 +35860,7 @@
         <v>1235</v>
       </c>
     </row>
-    <row r="279" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A279" s="1">
         <v>278</v>
       </c>
@@ -35893,7 +35892,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="280" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A280" s="1">
         <v>279</v>
       </c>
@@ -35925,7 +35924,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="281" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A281" s="1">
         <v>280</v>
       </c>
@@ -35957,7 +35956,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="282" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A282" s="1">
         <v>281</v>
       </c>
@@ -35989,7 +35988,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="283" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A283" s="1">
         <v>282</v>
       </c>
@@ -36021,7 +36020,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="284" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A284" s="1">
         <v>283</v>
       </c>
@@ -36053,7 +36052,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="285" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A285" s="1">
         <v>284</v>
       </c>
@@ -36085,7 +36084,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="286" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A286" s="1">
         <v>285</v>
       </c>
@@ -36117,7 +36116,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="287" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A287" s="1">
         <v>286</v>
       </c>
@@ -36149,7 +36148,7 @@
         <v>1288</v>
       </c>
     </row>
-    <row r="288" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A288" s="1">
         <v>287</v>
       </c>
@@ -36181,7 +36180,7 @@
         <v>1637</v>
       </c>
     </row>
-    <row r="289" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A289" s="1">
         <v>288</v>
       </c>
@@ -36213,7 +36212,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="290" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A290" s="1">
         <v>289</v>
       </c>
@@ -36245,7 +36244,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="291" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A291" s="1">
         <v>290</v>
       </c>
@@ -36277,7 +36276,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="292" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A292" s="1">
         <v>291</v>
       </c>
@@ -36309,7 +36308,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="293" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A293" s="1">
         <v>292</v>
       </c>
@@ -36341,7 +36340,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="294" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A294" s="1">
         <v>293</v>
       </c>
@@ -36373,7 +36372,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="295" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A295" s="1">
         <v>294</v>
       </c>
@@ -36405,7 +36404,7 @@
         <v>1646</v>
       </c>
     </row>
-    <row r="296" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A296" s="1">
         <v>295</v>
       </c>
@@ -36437,7 +36436,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="297" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A297" s="1">
         <v>296</v>
       </c>
@@ -37301,7 +37300,7 @@
         <v>1463</v>
       </c>
     </row>
-    <row r="324" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A324" s="1">
         <v>323</v>
       </c>
@@ -37333,7 +37332,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="325" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A325" s="1">
         <v>324</v>
       </c>
@@ -37365,7 +37364,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="326" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A326" s="1">
         <v>325</v>
       </c>
@@ -37397,7 +37396,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="327" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A327" s="1">
         <v>326</v>
       </c>
@@ -37429,7 +37428,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="328" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A328" s="1">
         <v>327</v>
       </c>
@@ -37461,7 +37460,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="329" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A329" s="1">
         <v>328</v>
       </c>
@@ -37493,7 +37492,7 @@
         <v>1210</v>
       </c>
     </row>
-    <row r="330" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A330" s="1">
         <v>329</v>
       </c>
@@ -37525,7 +37524,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="331" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A331" s="1">
         <v>330</v>
       </c>
@@ -37557,7 +37556,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="332" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A332" s="1">
         <v>331</v>
       </c>
@@ -37589,7 +37588,7 @@
         <v>1227</v>
       </c>
     </row>
-    <row r="333" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A333" s="1">
         <v>332</v>
       </c>
@@ -37621,7 +37620,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="334" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A334" s="1">
         <v>333</v>
       </c>
@@ -37653,7 +37652,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="335" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A335" s="1">
         <v>334</v>
       </c>
@@ -37685,7 +37684,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="336" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A336" s="1">
         <v>335</v>
       </c>
@@ -37717,7 +37716,7 @@
         <v>1650</v>
       </c>
     </row>
-    <row r="337" spans="1:10" hidden="1" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A337" s="1">
         <v>336</v>
       </c>
@@ -37750,13 +37749,7 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J337" xr:uid="{00000000-0001-0000-0200-000000000000}">
-    <filterColumn colId="1">
-      <filters>
-        <filter val="Nagamas Motor"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:J337" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>